--- a/data/huanchaquito.xlsx
+++ b/data/huanchaquito.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,25 +462,40 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -508,18 +523,27 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="n">
         <v>8</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -542,21 +566,30 @@
         <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
       </c>
       <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
         <v>9</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>6</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -579,21 +612,30 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -619,18 +661,27 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
+      <c r="K5" t="n">
         <v>8</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>14</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -653,21 +704,30 @@
         <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>7</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>6</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -690,23 +750,32 @@
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
       </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -727,21 +796,30 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>5</v>
       </c>
-      <c r="H8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>7</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -764,21 +842,30 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J9" t="n">
         <v>3</v>
       </c>
       <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -801,23 +888,32 @@
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>6</v>
       </c>
       <c r="K10" t="n">
         <v>6</v>
       </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -838,21 +934,30 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" t="n">
         <v>5</v>
       </c>
-      <c r="K11" t="n">
+      <c r="N11" t="n">
         <v>5</v>
       </c>
     </row>
@@ -875,21 +980,30 @@
         <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
+      <c r="K12" t="n">
         <v>8</v>
       </c>
-      <c r="I12" t="n">
+      <c r="L12" t="n">
         <v>6</v>
       </c>
-      <c r="J12" t="n">
+      <c r="M12" t="n">
         <v>4</v>
       </c>
-      <c r="K12" t="n">
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -912,21 +1026,30 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
+      <c r="K13" t="n">
         <v>6</v>
       </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
         <v>4</v>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
         <v>6</v>
       </c>
-      <c r="K13" t="n">
+      <c r="N13" t="n">
         <v>10</v>
       </c>
     </row>
@@ -952,18 +1075,27 @@
         <v>11</v>
       </c>
       <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>5</v>
-      </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -986,21 +1118,30 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>10</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" t="n">
         <v>4</v>
       </c>
-      <c r="J15" t="n">
+      <c r="M15" t="n">
         <v>5</v>
       </c>
-      <c r="K15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1026,18 +1167,27 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
-        <v>10</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1060,21 +1210,30 @@
         <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
+      <c r="K17" t="n">
         <v>9</v>
       </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
         <v>9</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1097,21 +1256,30 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
+      <c r="K18" t="n">
         <v>7</v>
       </c>
-      <c r="I18" t="n">
+      <c r="L18" t="n">
         <v>5</v>
       </c>
-      <c r="J18" t="n">
+      <c r="M18" t="n">
         <v>5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1134,21 +1302,30 @@
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>5</v>
       </c>
-      <c r="H19" t="n">
-        <v>10</v>
-      </c>
-      <c r="I19" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" t="n">
+        <v>10</v>
+      </c>
+      <c r="M19" t="n">
         <v>7</v>
       </c>
-      <c r="K19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1174,18 +1351,27 @@
         <v>7</v>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>3</v>
       </c>
-      <c r="H20" t="n">
+      <c r="K20" t="n">
         <v>8</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>14</v>
       </c>
-      <c r="K20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1208,21 +1394,30 @@
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="H21" t="n">
+      <c r="K21" t="n">
         <v>8</v>
       </c>
-      <c r="I21" t="n">
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="n">
+      <c r="M21" t="n">
         <v>6</v>
       </c>
-      <c r="K21" t="n">
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1237,7 +1432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,25 +1468,40 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1324,19 +1534,34 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1360,7 +1585,11 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>3</t>
@@ -1368,16 +1597,31 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1409,20 +1653,31 @@
           <t>6</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1449,21 +1704,32 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1495,28 +1761,43 @@
           <t>8</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1544,24 +1825,35 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1593,28 +1885,43 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1640,26 +1947,37 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1687,28 +2005,39 @@
           <t>9</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1740,28 +2069,43 @@
           <t>6</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1793,28 +2137,39 @@
           <t>4</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1842,28 +2197,47 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1894,17 +2268,28 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1936,28 +2321,43 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1974,23 +2374,26 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2018,24 +2421,31 @@
           <t>9</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2067,28 +2477,43 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -2116,28 +2541,43 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2170,23 +2610,30 @@
           <t>7</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2218,28 +2665,43 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/huanchaquito.xlsx
+++ b/data/huanchaquito.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,25 +477,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -529,21 +539,27 @@
         <v>15</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="n">
         <v>8</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -578,18 +594,24 @@
         <v>8</v>
       </c>
       <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>3</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>9</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>6</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -624,18 +646,24 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -670,18 +698,24 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>8</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>14</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -704,7 +738,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>7</v>
@@ -713,23 +747,29 @@
         <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5</v>
       </c>
       <c r="N6" t="n">
         <v>6</v>
       </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -759,21 +799,27 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>5</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>4</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -805,21 +851,27 @@
         <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>5</v>
       </c>
-      <c r="K8" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -851,21 +903,27 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="n">
-        <v>10</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -897,21 +955,27 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>4</v>
       </c>
       <c r="M10" t="n">
         <v>6</v>
       </c>
       <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -946,18 +1010,24 @@
         <v>7</v>
       </c>
       <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>8</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>7</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
     </row>
@@ -989,21 +1059,27 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>8</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>6</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>4</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1035,21 +1111,27 @@
         <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
       </c>
       <c r="M13" t="n">
         <v>6</v>
       </c>
       <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6</v>
+      </c>
+      <c r="P13" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1084,18 +1166,24 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>4</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1130,18 +1218,24 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
+        <v>14</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>10</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" t="n">
         <v>4</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>5</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1176,18 +1270,24 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>10</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
+        <v>10</v>
+      </c>
+      <c r="N16" t="n">
         <v>5</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1219,21 +1319,27 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
+        <v>13</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>9</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>9</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1268,18 +1374,24 @@
         <v>9</v>
       </c>
       <c r="J18" t="n">
+        <v>12</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>7</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>5</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>5</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1311,21 +1423,27 @@
         <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
+        <v>13</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>5</v>
       </c>
-      <c r="K19" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" t="n">
-        <v>10</v>
-      </c>
       <c r="M19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N19" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" t="n">
         <v>7</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1360,18 +1478,24 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
+        <v>22</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>3</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>14</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1403,21 +1527,27 @@
         <v>10</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>2</v>
       </c>
       <c r="M21" t="n">
+        <v>8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
         <v>6</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1432,7 +1562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1483,25 +1613,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1546,22 +1686,24 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1607,21 +1749,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1667,17 +1815,23 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1713,23 +1867,29 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1763,41 +1923,51 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1836,24 +2006,34 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1900,28 +2080,38 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1958,26 +2148,28 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2016,28 +2208,38 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2087,25 +2289,35 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2148,28 +2360,38 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2214,30 +2436,36 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2277,19 +2505,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2339,25 +2569,31 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2377,23 +2613,25 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2428,24 +2666,34 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2495,25 +2743,31 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -2556,28 +2810,38 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2619,21 +2883,27 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2680,28 +2950,38 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/huanchaquito.xlsx
+++ b/data/huanchaquito.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,25 +487,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -551,15 +556,18 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" t="n">
         <v>8</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -597,21 +605,24 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>3</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>9</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
       <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>6</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -652,18 +663,21 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>2</v>
       </c>
-      <c r="M4" t="n">
-        <v>10</v>
-      </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -701,21 +715,24 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>8</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>14</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -753,21 +770,24 @@
         <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>7</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>6</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>5</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -805,21 +825,24 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>5</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>4</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -857,21 +880,24 @@
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>5</v>
       </c>
-      <c r="M8" t="n">
-        <v>10</v>
-      </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
         <v>7</v>
       </c>
       <c r="P8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -912,18 +938,21 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
         <v>3</v>
       </c>
-      <c r="M9" t="n">
-        <v>10</v>
-      </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>3</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -961,23 +990,26 @@
         <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>6</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>6</v>
       </c>
       <c r="P10" t="n">
         <v>6</v>
       </c>
+      <c r="Q10" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1013,23 +1045,26 @@
         <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>8</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>5</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
       </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1065,21 +1100,24 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>8</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>6</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>4</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1117,21 +1155,24 @@
         <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>6</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>4</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>6</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1172,18 +1213,21 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" t="n">
         <v>2</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>4</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1221,21 +1265,24 @@
         <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>2</v>
       </c>
-      <c r="M15" t="n">
-        <v>10</v>
-      </c>
       <c r="N15" t="n">
+        <v>10</v>
+      </c>
+      <c r="O15" t="n">
         <v>4</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>5</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1276,18 +1323,21 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>10</v>
-      </c>
       <c r="N16" t="n">
+        <v>10</v>
+      </c>
+      <c r="O16" t="n">
         <v>5</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1328,18 +1378,21 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>9</v>
       </c>
       <c r="N17" t="n">
         <v>9</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1377,21 +1430,24 @@
         <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>2</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>7</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>5</v>
       </c>
       <c r="P18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1429,21 +1485,24 @@
         <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>5</v>
       </c>
-      <c r="M19" t="n">
-        <v>10</v>
-      </c>
       <c r="N19" t="n">
         <v>10</v>
       </c>
       <c r="O19" t="n">
+        <v>10</v>
+      </c>
+      <c r="P19" t="n">
         <v>7</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1481,21 +1540,24 @@
         <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>8</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>14</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1533,21 +1595,24 @@
         <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>8</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>2</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>6</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1562,7 +1627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,25 +1688,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1692,18 +1762,19 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1752,24 +1823,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1819,19 +1895,20 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1870,26 +1947,27 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1946,28 +2024,33 @@
           <t>7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2016,24 +2099,29 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2090,28 +2178,33 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2155,21 +2248,26 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2218,28 +2316,33 @@
           <t>7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2294,30 +2397,31 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2370,28 +2474,33 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2444,28 +2553,33 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2509,17 +2623,22 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2572,28 +2691,33 @@
           <t>14</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2615,23 +2739,24 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2677,23 +2802,24 @@
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2746,28 +2872,33 @@
           <t>12</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -2820,17 +2951,17 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>10</t>
@@ -2838,10 +2969,15 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2886,24 +3022,29 @@
           <t>22</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2960,28 +3101,33 @@
           <t>12</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/huanchaquito.xlsx
+++ b/data/huanchaquito.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,25 +492,30 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -559,15 +564,18 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P2" t="n">
         <v>8</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -605,24 +613,27 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>3</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>9</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>6</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -663,21 +674,24 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" t="n">
-        <v>10</v>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -721,18 +735,21 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>8</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>14</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -773,21 +790,24 @@
         <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>3</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>7</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>6</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -828,21 +848,24 @@
         <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>3</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>5</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -883,21 +906,24 @@
         <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>5</v>
       </c>
-      <c r="N8" t="n">
-        <v>10</v>
-      </c>
       <c r="O8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
         <v>7</v>
       </c>
       <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -938,21 +964,24 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>3</v>
       </c>
-      <c r="N9" t="n">
-        <v>10</v>
-      </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -996,20 +1025,23 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>6</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>6</v>
       </c>
       <c r="Q10" t="n">
         <v>6</v>
       </c>
+      <c r="R10" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1048,23 +1080,26 @@
         <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>8</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>7</v>
-      </c>
-      <c r="P11" t="n">
-        <v>5</v>
       </c>
       <c r="Q11" t="n">
         <v>5</v>
       </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1106,18 +1141,21 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>8</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1158,21 +1196,24 @@
         <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>2</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>6</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>4</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>6</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1216,18 +1257,21 @@
         <v>6</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>2</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>4</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1268,21 +1312,24 @@
         <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>2</v>
       </c>
-      <c r="N15" t="n">
-        <v>10</v>
-      </c>
       <c r="O15" t="n">
+        <v>10</v>
+      </c>
+      <c r="P15" t="n">
         <v>4</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>5</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1326,18 +1373,21 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
-        <v>10</v>
-      </c>
       <c r="O16" t="n">
+        <v>10</v>
+      </c>
+      <c r="P16" t="n">
         <v>5</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
       <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1378,21 +1428,24 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>9</v>
       </c>
       <c r="O17" t="n">
         <v>9</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1403,7 +1456,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
         <v>13</v>
@@ -1433,21 +1486,24 @@
         <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>2</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>7</v>
-      </c>
-      <c r="O18" t="n">
-        <v>5</v>
       </c>
       <c r="P18" t="n">
         <v>5</v>
       </c>
       <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1488,21 +1544,24 @@
         <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>5</v>
       </c>
-      <c r="N19" t="n">
-        <v>10</v>
-      </c>
       <c r="O19" t="n">
         <v>10</v>
       </c>
       <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="n">
         <v>7</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1546,18 +1605,21 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>3</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>8</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
       <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>14</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1598,21 +1660,24 @@
         <v>12</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>2</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>8</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>2</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>6</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1627,7 +1692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1693,25 +1758,30 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1763,18 +1833,19 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1823,29 +1894,30 @@
           <t>5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1895,20 +1967,25 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1953,21 +2030,26 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2029,28 +2111,33 @@
           <t>3</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2104,24 +2191,29 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2183,28 +2275,33 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2248,26 +2345,27 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2322,27 +2420,28 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2400,28 +2499,33 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2480,27 +2584,28 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2558,28 +2663,33 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2626,19 +2736,20 @@
           <t>6</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2696,28 +2807,33 @@
           <t>3</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2740,23 +2856,24 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O16" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2802,24 +2919,29 @@
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2833,7 +2955,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2877,28 +2999,33 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -2956,17 +3083,17 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>10</t>
@@ -2974,10 +3101,15 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3028,23 +3160,24 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3106,28 +3239,33 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/huanchaquito.xlsx
+++ b/data/huanchaquito.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,25 +497,40 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -561,21 +576,30 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>10</v>
+      </c>
+      <c r="S2" t="n">
         <v>8</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -622,18 +646,27 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>9</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>6</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -650,7 +683,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>6</v>
@@ -677,21 +710,30 @@
         <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>9</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
-        <v>10</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
+        <v>10</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -735,21 +777,30 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>8</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>14</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -796,18 +847,27 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>7</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -854,20 +914,29 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>5</v>
-      </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
         <v>5</v>
       </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -909,21 +978,30 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>5</v>
       </c>
-      <c r="O8" t="n">
-        <v>10</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
+        <v>10</v>
+      </c>
+      <c r="S8" t="n">
         <v>7</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>7</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -967,13 +1045,13 @@
         <v>13</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -982,6 +1060,15 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1025,23 +1112,32 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>6</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6</v>
       </c>
       <c r="R10" t="n">
         <v>6</v>
       </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1083,21 +1179,30 @@
         <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
         <v>8</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>7</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1108,7 +1213,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
@@ -1141,21 +1246,30 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
+        <v>10</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>6</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1199,21 +1313,30 @@
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
+        <v>9</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
         <v>6</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>6</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1260,18 +1383,27 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
+        <v>25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>15</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
         <v>4</v>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1315,21 +1447,30 @@
         <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>10</v>
+      </c>
+      <c r="S15" t="n">
         <v>4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
         <v>5</v>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1376,18 +1517,27 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="O16" t="n">
-        <v>10</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
+        <v>10</v>
+      </c>
+      <c r="S16" t="n">
         <v>5</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1434,18 +1584,27 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="O17" t="n">
+      <c r="R17" t="n">
         <v>9</v>
       </c>
-      <c r="P17" t="n">
+      <c r="S17" t="n">
         <v>9</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1492,18 +1651,27 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" t="n">
         <v>2</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
         <v>7</v>
       </c>
-      <c r="P18" t="n">
+      <c r="S18" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="T18" t="n">
         <v>5</v>
       </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1547,21 +1715,30 @@
         <v>13</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N19" t="n">
+        <v>11</v>
+      </c>
+      <c r="O19" t="n">
+        <v>10</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>5</v>
       </c>
-      <c r="O19" t="n">
-        <v>10</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>10</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1608,18 +1785,27 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3</v>
       </c>
-      <c r="O20" t="n">
+      <c r="R20" t="n">
         <v>8</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
         <v>14</v>
       </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1666,18 +1852,27 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
+        <v>7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="O21" t="n">
+      <c r="R21" t="n">
         <v>8</v>
       </c>
-      <c r="P21" t="n">
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="T21" t="n">
         <v>6</v>
       </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1692,7 +1887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,25 +1958,40 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1832,20 +2042,31 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1901,23 +2122,30 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1941,7 +2169,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1972,20 +2200,35 @@
           <t>5</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -2030,26 +2273,33 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2119,25 +2369,36 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2197,23 +2458,30 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2280,28 +2548,43 @@
           <t>10</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2348,24 +2631,35 @@
           <t>13</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2420,28 +2714,39 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2504,28 +2809,43 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2539,7 +2859,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2584,7 +2904,11 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>1</t>
@@ -2592,20 +2916,31 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2668,28 +3003,43 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2739,17 +3089,32 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -2812,28 +3177,39 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2857,23 +3233,26 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2925,23 +3304,26 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3007,25 +3389,36 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -3088,28 +3481,43 @@
           <t>13</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3163,21 +3571,28 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3247,25 +3662,32 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/huanchaquito.xlsx
+++ b/data/huanchaquito.xlsx
@@ -585,7 +585,7 @@
         <v>11</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>3</v>
@@ -707,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
@@ -719,7 +719,7 @@
         <v>9</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -786,7 +786,7 @@
         <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
@@ -853,7 +853,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
@@ -884,7 +884,7 @@
         <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
@@ -920,7 +920,7 @@
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="n">
         <v>3</v>
@@ -987,7 +987,7 @@
         <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
         <v>3</v>
@@ -1121,7 +1121,7 @@
         <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
         <v>3</v>
@@ -1322,7 +1322,7 @@
         <v>7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
         <v>2</v>
@@ -1389,7 +1389,7 @@
         <v>15</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
@@ -1456,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
         <v>2</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
@@ -1657,7 +1657,7 @@
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
@@ -1724,7 +1724,7 @@
         <v>10</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q19" t="n">
         <v>5</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q20" t="n">
         <v>3</v>
@@ -1843,7 +1843,7 @@
         <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L21" t="n">
         <v>2</v>
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
@@ -2053,7 +2053,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
@@ -2128,7 +2132,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>3</t>
@@ -2197,7 +2205,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2215,7 +2223,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>2</t>
@@ -2282,7 +2294,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>3</t>
@@ -2377,7 +2393,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>3</t>
@@ -2418,7 +2438,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2439,7 +2459,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2464,7 +2484,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>3</t>
@@ -2563,7 +2587,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>5</t>
@@ -2642,7 +2670,11 @@
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>3</t>
@@ -2725,7 +2757,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>3</t>
@@ -3018,7 +3054,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>2</t>
@@ -3099,7 +3139,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -3188,7 +3228,11 @@
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>2</t>
@@ -3306,7 +3350,11 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>2</t>
@@ -3397,7 +3445,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>2</t>
@@ -3496,7 +3548,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>5</t>
@@ -3575,7 +3631,11 @@
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>3</t>
@@ -3651,7 +3711,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3666,7 +3726,11 @@
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>2</t>
